--- a/data/trans_orig/IP1001-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP1001-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>519</t>
+          <t>518</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4257</t>
+          <t>4275</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4973</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1056</t>
+          <t>1061</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6607</t>
+          <t>6632</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,88%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>48311</t>
+          <t>48293</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>52049</t>
+          <t>52050</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,9%</t>
+          <t>91,87%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>55244</t>
+          <t>55313</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,74%</t>
+          <t>91,86%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>106178</t>
+          <t>106153</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>111729</t>
+          <t>111724</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>94,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1076,47 +1076,47 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>1284</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>8514</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>4,08%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>1,26%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>8,38%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>3471</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
           <t>1300</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>8954</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>4,08%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>1,28%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>8,82%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>3471</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>1295</t>
-        </is>
-      </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8169</t>
+          <t>8313</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3996</t>
+          <t>4122</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13299</t>
+          <t>13270</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,31%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>92608</t>
+          <t>93048</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>100262</t>
+          <t>100278</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,18%</t>
+          <t>91,62%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>100588</t>
+          <t>100444</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>107462</t>
+          <t>107457</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>92,36%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>197020</t>
+          <t>197049</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>206323</t>
+          <t>206197</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>93,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,04%</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3154</t>
+          <t>3446</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4308</t>
+          <t>3804</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>609</t>
+          <t>607</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5187</t>
+          <t>5659</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>4,1%</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>64443</t>
+          <t>64151</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>94,9%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>66019</t>
+          <t>66523</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>94,59%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>132737</t>
+          <t>132265</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>137315</t>
+          <t>137317</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>552</t>
+          <t>1049</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6602</t>
+          <t>7198</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>821</t>
+          <t>810</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6506</t>
+          <t>7608</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2598</t>
+          <t>2309</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10747</t>
+          <t>10284</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>6,68%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>68259</t>
+          <t>67663</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>74309</t>
+          <t>73812</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,18%</t>
+          <t>90,38%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>72605</t>
+          <t>71503</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>78290</t>
+          <t>78301</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,78%</t>
+          <t>90,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>143225</t>
+          <t>143688</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>151374</t>
+          <t>151663</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,02%</t>
+          <t>93,32%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,5%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1357</t>
+          <t>1915</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8083</t>
+          <t>8231</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>668</t>
+          <t>664</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4989</t>
+          <t>5279</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2800</t>
+          <t>3367</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>10741</t>
+          <t>11217</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,94%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>33769</t>
+          <t>33621</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>40495</t>
+          <t>39937</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>80,69%</t>
+          <t>80,33%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>39854</t>
+          <t>39564</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>44175</t>
+          <t>44179</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,88%</t>
+          <t>88,23%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>75954</t>
+          <t>75478</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>83895</t>
+          <t>83328</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,61%</t>
+          <t>87,06%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,12%</t>
         </is>
       </c>
     </row>
@@ -2453,7 +2453,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5507</t>
+          <t>5865</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>571</t>
+          <t>573</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5518</t>
+          <t>4999</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1369</t>
+          <t>1757</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7834</t>
+          <t>7877</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,8%</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>50548</t>
+          <t>50190</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>90,18%</t>
+          <t>89,54%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>54214</t>
+          <t>54733</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>59161</t>
+          <t>59159</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>90,76%</t>
+          <t>91,63%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>107953</t>
+          <t>107910</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>114418</t>
+          <t>114030</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,23%</t>
+          <t>93,2%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,48%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>685</t>
+          <t>686</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5729</t>
+          <t>5733</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3887</t>
+          <t>3910</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2846,7 +2846,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1337</t>
+          <t>1339</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>7428</t>
+          <t>7633</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,89%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>122893</t>
+          <t>122889</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>127937</t>
+          <t>127936</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,7 +2919,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,54%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2939,7 +2939,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>131768</t>
+          <t>131745</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>256849</t>
+          <t>256644</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>262940</t>
+          <t>262938</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1217</t>
+          <t>1094</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7188</t>
+          <t>7096</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2346</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>9748</t>
+          <t>9491</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,47 +3184,47 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
+          <t>1,45%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>5,79%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>8242</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>4605</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>14242</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>2,56%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
           <t>1,43%</t>
         </is>
       </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>5,94%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>8242</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>4360</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>13423</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>2,56%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>1,35%</t>
-        </is>
-      </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,42%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>150716</t>
+          <t>150808</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>156687</t>
+          <t>156810</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>154310</t>
+          <t>154567</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>161712</t>
+          <t>161679</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,47 +3297,47 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>94,21%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
+          <t>98,55%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>481</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>313720</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>307720</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>317357</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>97,44%</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>95,58%</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
           <t>98,57%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>481</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>313720</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>308539</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>317602</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>97,44%</t>
-        </is>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>95,83%</t>
-        </is>
-      </c>
-      <c r="W26" s="2" t="inlineStr">
-        <is>
-          <t>98,65%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>13883</t>
+          <t>14626</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>28151</t>
+          <t>28995</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>13233</t>
+          <t>13052</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>27208</t>
+          <t>27270</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>30612</t>
+          <t>30674</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>50416</t>
+          <t>50444</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,7 +3562,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>652870</t>
+          <t>652026</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>667138</t>
+          <t>666395</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>695492</t>
+          <t>695430</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>709467</t>
+          <t>709648</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,23%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1353305</t>
+          <t>1353277</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1373109</t>
+          <t>1373047</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,81%</t>
         </is>
       </c>
     </row>
@@ -4061,7 +4061,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3428</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4076,7 +4076,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>554</t>
+          <t>553</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4997</t>
+          <t>5010</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4111,7 +4111,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>616</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5427</t>
+          <t>6059</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>5,3%</t>
         </is>
       </c>
     </row>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>49536</t>
+          <t>49930</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -4184,7 +4184,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>94,27%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>56380</t>
+          <t>56367</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>60823</t>
+          <t>60824</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,7 +4219,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,86%</t>
+          <t>91,84%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>108914</t>
+          <t>108282</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>113753</t>
+          <t>113725</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>94,7%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,46%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>917</t>
+          <t>702</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7273</t>
+          <t>7504</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1868</t>
+          <t>1904</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10653</t>
+          <t>9821</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4160</t>
+          <t>4152</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>14418</t>
+          <t>14636</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,78%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>97440</t>
+          <t>97209</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>103796</t>
+          <t>104011</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,05%</t>
+          <t>92,83%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>100506</t>
+          <t>101338</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>109291</t>
+          <t>109255</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,42%</t>
+          <t>91,17%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>201454</t>
+          <t>201236</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>211712</t>
+          <t>211720</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>93,22%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>98,08%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>676</t>
+          <t>679</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5845</t>
+          <t>5704</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>645</t>
+          <t>642</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5375</t>
+          <t>5382</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4797,7 +4797,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1402</t>
+          <t>1995</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8353</t>
+          <t>8999</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,49%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>62333</t>
+          <t>62474</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>67502</t>
+          <t>67499</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,43%</t>
+          <t>91,63%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>65209</t>
+          <t>65202</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>69939</t>
+          <t>69942</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,7 +4905,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>92,37%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>130409</t>
+          <t>129763</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>137360</t>
+          <t>136767</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>93,51%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>98,56%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>873</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6955</t>
+          <t>6736</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>627</t>
+          <t>636</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5784</t>
+          <t>6495</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2153</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9942</t>
+          <t>9582</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>5,99%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>70806</t>
+          <t>71025</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>77146</t>
+          <t>76888</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,06%</t>
+          <t>91,34%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>76450</t>
+          <t>75739</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>81607</t>
+          <t>81598</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>92,1%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>150053</t>
+          <t>150413</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>157969</t>
+          <t>157842</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>94,01%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,65%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>933</t>
+          <t>904</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7653</t>
+          <t>7475</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5468,7 +5468,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3427</t>
+          <t>3440</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5483,7 +5483,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1494</t>
+          <t>1553</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>8718</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>9,69%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>36248</t>
+          <t>36426</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>42968</t>
+          <t>42997</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>82,57%</t>
+          <t>82,97%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,7 +5576,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>42678</t>
+          <t>42665</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -5591,7 +5591,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>92,54%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>81005</t>
+          <t>81288</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>88512</t>
+          <t>88453</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,0%</t>
+          <t>90,31%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,27%</t>
         </is>
       </c>
     </row>
@@ -5811,7 +5811,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4358</t>
+          <t>4296</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5826,7 +5826,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5846,7 +5846,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4392</t>
+          <t>4373</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5861,7 +5861,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,76%</t>
         </is>
       </c>
     </row>
@@ -5919,7 +5919,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>55887</t>
+          <t>55949</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -5934,7 +5934,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>92,87%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -5954,7 +5954,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>111838</t>
+          <t>111857</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -5969,7 +5969,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -6119,7 +6119,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4710</t>
+          <t>4757</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6134,7 +6134,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6154,7 +6154,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3350</t>
+          <t>3277</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6169,7 +6169,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>648</t>
+          <t>647</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5547</t>
+          <t>5399</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6204,7 +6204,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,9%</t>
         </is>
       </c>
     </row>
@@ -6227,7 +6227,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>134008</t>
+          <t>133961</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -6242,7 +6242,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,57%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -6262,7 +6262,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>142389</t>
+          <t>142462</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -6277,7 +6277,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>278910</t>
+          <t>279058</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>283809</t>
+          <t>283810</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,7 +6312,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -6462,7 +6462,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2935</t>
+          <t>3952</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6477,7 +6477,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3374</t>
+          <t>3293</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>11799</t>
+          <t>11606</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3567</t>
+          <t>3482</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>12471</t>
+          <t>11781</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,51%</t>
         </is>
       </c>
     </row>
@@ -6570,7 +6570,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>161773</t>
+          <t>160756</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -6585,7 +6585,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>159516</t>
+          <t>159709</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>167941</t>
+          <t>168022</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>93,11%</t>
+          <t>93,23%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>323552</t>
+          <t>324242</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>332456</t>
+          <t>332541</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,96%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>8489</t>
+          <t>7856</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>20761</t>
+          <t>20292</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>14034</t>
+          <t>13431</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>28950</t>
+          <t>28854</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>24805</t>
+          <t>24619</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>44239</t>
+          <t>44180</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,03%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>686167</t>
+          <t>686636</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>698439</t>
+          <t>699072</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>719808</t>
+          <t>719904</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>734724</t>
+          <t>735327</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1411447</t>
+          <t>1411506</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1430881</t>
+          <t>1431067</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,31%</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>636</t>
+          <t>635</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6264</t>
+          <t>6069</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7399,7 +7399,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7419,7 +7419,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4868</t>
+          <t>4971</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7434,7 +7434,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1455</t>
+          <t>1634</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8288</t>
+          <t>8362</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,86%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>51107</t>
+          <t>51302</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>56735</t>
+          <t>56736</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,7 +7507,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,08%</t>
+          <t>89,42%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -7527,7 +7527,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>59594</t>
+          <t>59491</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -7542,7 +7542,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>92,29%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>113545</t>
+          <t>113471</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>120378</t>
+          <t>120199</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>93,14%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,66%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>654</t>
+          <t>662</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5859</t>
+          <t>6014</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,47 +7737,47 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
+          <t>0,64%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>5,79%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>2149</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>690</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>5751</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>1,95%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
           <t>0,63%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>5,64%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>2149</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>696</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>6471</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,95%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,63%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2033</t>
+          <t>1966</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9563</t>
+          <t>9111</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,25%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>98088</t>
+          <t>97933</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>103293</t>
+          <t>103285</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,49 +7850,49 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>94,21%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
+          <t>99,36%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>108134</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>104532</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>109593</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>98,05%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>94,78%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
           <t>99,37%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>158</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>108134</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>103812</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>109587</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>98,05%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>94,13%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>99,37%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>311</t>
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>204667</t>
+          <t>205119</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>212197</t>
+          <t>212264</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,08%</t>
         </is>
       </c>
     </row>
@@ -8105,7 +8105,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2955</t>
+          <t>3663</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>731</t>
+          <t>729</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6858</t>
+          <t>6101</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8155,7 +8155,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,46%</t>
         </is>
       </c>
     </row>
@@ -8213,7 +8213,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>66950</t>
+          <t>66242</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -8228,7 +8228,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>94,76%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>129878</t>
+          <t>130635</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>136005</t>
+          <t>136007</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,7 +8263,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>95,54%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1714</t>
+          <t>1400</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7787</t>
+          <t>7705</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2520</t>
+          <t>2698</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9994</t>
+          <t>10719</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4918</t>
+          <t>5170</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>15204</t>
+          <t>14582</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,22%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>69174</t>
+          <t>69256</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>75247</t>
+          <t>75561</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,88%</t>
+          <t>89,99%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>71190</t>
+          <t>70465</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>78664</t>
+          <t>78486</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,69%</t>
+          <t>86,8%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>142941</t>
+          <t>143563</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>153227</t>
+          <t>152975</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,39%</t>
+          <t>90,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,73%</t>
         </is>
       </c>
     </row>
@@ -8756,7 +8756,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5166</t>
+          <t>4751</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8771,7 +8771,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8791,7 +8791,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4799</t>
+          <t>4590</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8806,7 +8806,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>856</t>
+          <t>617</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>7063</t>
+          <t>6665</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,42%</t>
         </is>
       </c>
     </row>
@@ -8864,7 +8864,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>38272</t>
+          <t>38687</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -8879,7 +8879,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>88,11%</t>
+          <t>89,06%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -8899,7 +8899,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>41551</t>
+          <t>41760</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -8914,7 +8914,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,65%</t>
+          <t>90,1%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>82725</t>
+          <t>83123</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>88932</t>
+          <t>89171</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,13%</t>
+          <t>92,58%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,31%</t>
         </is>
       </c>
     </row>
@@ -9099,7 +9099,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5942</t>
+          <t>5859</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9114,7 +9114,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9169,7 +9169,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5765</t>
+          <t>5619</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9184,7 +9184,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,02%</t>
         </is>
       </c>
     </row>
@@ -9207,7 +9207,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>48331</t>
+          <t>48414</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -9222,7 +9222,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>89,05%</t>
+          <t>89,2%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -9277,7 +9277,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>106247</t>
+          <t>106393</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -9292,7 +9292,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>94,98%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -9442,7 +9442,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4334</t>
+          <t>4748</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9457,7 +9457,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>611</t>
+          <t>607</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>6062</t>
+          <t>5643</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9492,7 +9492,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1235</t>
+          <t>1174</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>7801</t>
+          <t>8116</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,88%</t>
         </is>
       </c>
     </row>
@@ -9550,7 +9550,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>133040</t>
+          <t>132626</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -9565,7 +9565,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>138010</t>
+          <t>138429</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>143461</t>
+          <t>143465</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,7 +9600,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>273645</t>
+          <t>273330</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>280211</t>
+          <t>280272</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,58%</t>
         </is>
       </c>
     </row>
@@ -9785,7 +9785,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4201</t>
+          <t>3808</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9800,7 +9800,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>2483</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>10189</t>
+          <t>10659</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3418</t>
+          <t>3511</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>11791</t>
+          <t>12155</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,63%</t>
         </is>
       </c>
     </row>
@@ -9893,7 +9893,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>159975</t>
+          <t>160368</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -9908,7 +9908,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>160660</t>
+          <t>160190</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>168246</t>
+          <t>168366</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>323234</t>
+          <t>322870</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>331607</t>
+          <t>331514</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,37%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>98,95%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>10432</t>
+          <t>10516</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>24039</t>
+          <t>23805</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>12716</t>
+          <t>13327</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>26725</t>
+          <t>27885</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>26154</t>
+          <t>25800</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>46007</t>
+          <t>44912</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,1%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>680332</t>
+          <t>680566</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>693939</t>
+          <t>693855</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>718119</t>
+          <t>716959</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>732128</t>
+          <t>731517</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1403208</t>
+          <t>1404303</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1423061</t>
+          <t>1423415</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,22%</t>
         </is>
       </c>
     </row>
@@ -10707,7 +10707,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3582</t>
+          <t>4038</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10722,7 +10722,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10777,7 +10777,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3849</t>
+          <t>4002</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10792,7 +10792,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,62%</t>
         </is>
       </c>
     </row>
@@ -10815,7 +10815,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>69700</t>
+          <t>69244</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -10830,7 +10830,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>94,49%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -10885,7 +10885,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>148799</t>
+          <t>148646</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -10900,7 +10900,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>969</t>
+          <t>859</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9024</t>
+          <t>8866</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1437</t>
+          <t>922</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8719</t>
+          <t>8399</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,3%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>117815</t>
+          <t>117973</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>125870</t>
+          <t>125980</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,89%</t>
+          <t>93,01%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>245716</t>
+          <t>246036</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>252998</t>
+          <t>253513</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,7%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,64%</t>
         </is>
       </c>
     </row>
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2591</t>
+          <t>2552</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11408</t>
+          <t>11576</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>17,24%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2147</t>
+          <t>2438</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11608</t>
+          <t>12372</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,86%</t>
         </is>
       </c>
     </row>
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>55755</t>
+          <t>55587</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>64572</t>
+          <t>64611</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,01%</t>
+          <t>82,76%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>113823</t>
+          <t>113059</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>123284</t>
+          <t>122993</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,75%</t>
+          <t>90,14%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,06%</t>
         </is>
       </c>
     </row>
@@ -12422,7 +12422,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4201</t>
+          <t>4156</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12437,7 +12437,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>906</t>
+          <t>889</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6083</t>
+          <t>6185</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1806</t>
+          <t>1707</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>8320</t>
+          <t>7895</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>7,71%</t>
         </is>
       </c>
     </row>
@@ -12530,7 +12530,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>41966</t>
+          <t>42011</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -12545,7 +12545,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>90,9%</t>
+          <t>91,0%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>50103</t>
+          <t>50001</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>55280</t>
+          <t>55297</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>89,17%</t>
+          <t>88,99%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>94033</t>
+          <t>94458</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>100547</t>
+          <t>100646</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>91,87%</t>
+          <t>92,29%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,33%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3606</t>
+          <t>3740</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>12362</t>
+          <t>13556</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>8307</t>
+          <t>8920</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>27373</t>
+          <t>26873</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>17,23%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>15288</t>
+          <t>14292</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>36680</t>
+          <t>36006</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>12,84%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>112146</t>
+          <t>110952</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>120902</t>
+          <t>120768</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>90,07%</t>
+          <t>89,11%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>97,0%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>128639</t>
+          <t>129139</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>147705</t>
+          <t>147092</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>82,45%</t>
+          <t>82,77%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>243840</t>
+          <t>244514</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>265232</t>
+          <t>266228</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>86,92%</t>
+          <t>87,16%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>94,91%</t>
         </is>
       </c>
     </row>
@@ -13108,7 +13108,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4651</t>
+          <t>3090</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13123,7 +13123,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>727</t>
+          <t>732</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>7238</t>
+          <t>6965</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1453</t>
+          <t>1436</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>7876</t>
+          <t>8182</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13193,7 +13193,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,84%</t>
         </is>
       </c>
     </row>
@@ -13216,7 +13216,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>126968</t>
+          <t>128529</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -13231,7 +13231,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>149557</t>
+          <t>149830</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>156068</t>
+          <t>156063</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,53%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>280538</t>
+          <t>280232</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>286961</t>
+          <t>286978</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,7 +13301,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>8708</t>
+          <t>8724</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>21961</t>
+          <t>21433</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13466,7 +13466,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>17244</t>
+          <t>18728</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>40171</t>
+          <t>41195</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>30329</t>
+          <t>30855</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>56621</t>
+          <t>58133</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,07%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>643379</t>
+          <t>643907</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>656632</t>
+          <t>656616</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,7 +13574,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>721801</t>
+          <t>720777</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>744728</t>
+          <t>743244</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>94,73%</t>
+          <t>94,59%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1370691</t>
+          <t>1369179</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1396983</t>
+          <t>1396457</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,84%</t>
         </is>
       </c>
     </row>
